--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-practitioner.xlsx
@@ -368,7 +368,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1333,7 +1333,7 @@
     <t>Practitioner.qualification.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1445,7 +1445,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
